--- a/backtest_runs/20260410_193731/by_symbol/SNBL/SNBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SNBL/SNBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-6368.64000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>93631.35999999999</v>
@@ -587,7 +587,7 @@
         <v>-205.4399999999956</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>93425.92</v>
@@ -633,7 +633,7 @@
         <v>-3132.959999999997</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>90292.95999999999</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>90292.95999999999</v>
@@ -863,7 +863,7 @@
         <v>-1848.959999999997</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>90498.40000000001</v>
@@ -909,7 +909,7 @@
         <v>-975.8400000000065</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>89522.56</v>
@@ -955,7 +955,7 @@
         <v>-256.8000000000036</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>89265.75999999999</v>
@@ -1093,7 +1093,7 @@
         <v>-462.2399999999993</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>88803.52</v>
@@ -1185,7 +1185,7 @@
         <v>-3492.479999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>87108.64000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-6420</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>81715.84</v>
@@ -1415,7 +1415,7 @@
         <v>-2003.040000000003</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>82845.75999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-1489.440000000014</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>82126.71999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-924.4799999999985</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>90498.40000000001</v>
